--- a/outputs/qc/qc_notes.xlsx
+++ b/outputs/qc/qc_notes.xlsx
@@ -445,7 +445,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>103.625887</v>
+        <v>103.625685</v>
       </c>
     </row>
     <row r="4">
@@ -485,7 +485,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4663</v>
+        <v>5045</v>
       </c>
     </row>
     <row r="8">
@@ -505,7 +505,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8.720000000000001</v>
+        <v>8.74</v>
       </c>
     </row>
   </sheetData>
